--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.63805826901194</v>
+        <v>5.62868446871444</v>
       </c>
       <c r="D2" t="n">
-        <v>8.549224499919742</v>
+        <v>1.389248981236958</v>
       </c>
       <c r="E2" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F2" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.47273212435308</v>
+        <v>4.139318970207375</v>
       </c>
       <c r="D3" t="n">
-        <v>9.735753123867148</v>
+        <v>1.582059882628412</v>
       </c>
       <c r="E3" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F3" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>19.50573023862728</v>
+        <v>3.169681163776933</v>
       </c>
       <c r="D4" t="n">
-        <v>7.633199716753602</v>
+        <v>1.24039495397246</v>
       </c>
       <c r="E4" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F4" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.37379926011813</v>
+        <v>1.848242379769196</v>
       </c>
       <c r="D5" t="n">
-        <v>12.62963620115269</v>
+        <v>2.052315882687312</v>
       </c>
       <c r="E5" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F5" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.09951857241987</v>
+        <v>4.566171768018229</v>
       </c>
       <c r="D6" t="n">
-        <v>3.299026810554071</v>
+        <v>0.5360918567150367</v>
       </c>
       <c r="E6" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F6" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.53693361433153</v>
+        <v>2.524751712328873</v>
       </c>
       <c r="D7" t="n">
-        <v>6.969811477380077</v>
+        <v>1.132594365074262</v>
       </c>
       <c r="E7" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F7" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.95168746090262</v>
+        <v>4.054649212396675</v>
       </c>
       <c r="D8" t="n">
-        <v>11.01135777277262</v>
+        <v>1.789345638075551</v>
       </c>
       <c r="E8" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F8" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.71848287014877</v>
+        <v>4.504253466399175</v>
       </c>
       <c r="D9" t="n">
-        <v>19.51368627159945</v>
+        <v>3.17097401913491</v>
       </c>
       <c r="E9" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F9" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.14727646196792</v>
+        <v>7.661432425069787</v>
       </c>
       <c r="D10" t="n">
-        <v>36.88156721182006</v>
+        <v>5.993254671920759</v>
       </c>
       <c r="E10" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F10" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.1652304044802</v>
+        <v>6.364349940728032</v>
       </c>
       <c r="D11" t="n">
-        <v>13.40878316482998</v>
+        <v>2.178927264284871</v>
       </c>
       <c r="E11" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F11" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.43053867028907</v>
+        <v>7.382462533921974</v>
       </c>
       <c r="D12" t="n">
-        <v>15.50806241927082</v>
+        <v>2.520060143131509</v>
       </c>
       <c r="E12" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F12" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>27.25161368125413</v>
+        <v>4.428387223203797</v>
       </c>
       <c r="D13" t="n">
-        <v>19.67873949247072</v>
+        <v>3.197795167526492</v>
       </c>
       <c r="E13" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F13" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.11099639156123</v>
+        <v>4.7305369136287</v>
       </c>
       <c r="D14" t="n">
-        <v>11.3338781541902</v>
+        <v>1.841755200055908</v>
       </c>
       <c r="E14" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F14" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>28.04283881549721</v>
+        <v>4.556961307518296</v>
       </c>
       <c r="D15" t="n">
-        <v>20.51083724386804</v>
+        <v>3.333011052128557</v>
       </c>
       <c r="E15" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F15" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>51.71752746039932</v>
+        <v>8.404098212314889</v>
       </c>
       <c r="D16" t="n">
-        <v>29.23004919498479</v>
+        <v>4.749882994185028</v>
       </c>
       <c r="E16" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F16" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>38.77039102357491</v>
+        <v>6.300188541330923</v>
       </c>
       <c r="D17" t="n">
-        <v>28.67265279321819</v>
+        <v>4.659306078897957</v>
       </c>
       <c r="E17" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F17" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>33.35624438690844</v>
+        <v>5.420389712872622</v>
       </c>
       <c r="D18" t="n">
-        <v>38.44284951480814</v>
+        <v>6.246963046156322</v>
       </c>
       <c r="E18" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F18" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>19.97054092282702</v>
+        <v>3.245212899959391</v>
       </c>
       <c r="D19" t="n">
-        <v>14.50748777968933</v>
+        <v>2.357466764199516</v>
       </c>
       <c r="E19" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F19" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>31.96163509259575</v>
+        <v>5.193765702546809</v>
       </c>
       <c r="D20" t="n">
-        <v>15.19951641287025</v>
+        <v>2.469921417091416</v>
       </c>
       <c r="E20" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F20" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>22.72157474925779</v>
+        <v>3.692255896754391</v>
       </c>
       <c r="D21" t="n">
-        <v>7.336212808082453</v>
+        <v>1.192134581313399</v>
       </c>
       <c r="E21" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F21" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>38.88938370814427</v>
+        <v>6.319524852573444</v>
       </c>
       <c r="D22" t="n">
-        <v>40.83430730864379</v>
+        <v>6.635574937654617</v>
       </c>
       <c r="E22" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F22" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>30.33968937932611</v>
+        <v>4.930199524140493</v>
       </c>
       <c r="D23" t="n">
-        <v>6.330271033801065</v>
+        <v>1.028669042992673</v>
       </c>
       <c r="E23" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F23" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>24.27737461681441</v>
+        <v>3.945073375232341</v>
       </c>
       <c r="D24" t="n">
-        <v>22.79966041184166</v>
+        <v>3.70494481692427</v>
       </c>
       <c r="E24" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F24" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>43.3201162744303</v>
+        <v>7.039518894594924</v>
       </c>
       <c r="D25" t="n">
-        <v>39.43952401257524</v>
+        <v>6.408922652043477</v>
       </c>
       <c r="E25" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F25" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>10.4808311030054</v>
+        <v>1.703135054238378</v>
       </c>
       <c r="D26" t="n">
-        <v>10.87055120886847</v>
+        <v>1.766464571441126</v>
       </c>
       <c r="E26" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F26" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>22.34023088170354</v>
+        <v>3.630287518276825</v>
       </c>
       <c r="D27" t="n">
-        <v>23.29090540159295</v>
+        <v>3.784772127758855</v>
       </c>
       <c r="E27" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F27" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>32.22256236829451</v>
+        <v>5.236166384847858</v>
       </c>
       <c r="D28" t="n">
-        <v>32.82337645099265</v>
+        <v>5.333798673286306</v>
       </c>
       <c r="E28" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F28" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>14.88328778961292</v>
+        <v>2.418534265812099</v>
       </c>
       <c r="D29" t="n">
-        <v>24.57281326703288</v>
+        <v>3.993082155892843</v>
       </c>
       <c r="E29" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F29" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>1.155245903043095</v>
+        <v>0.187727459244503</v>
       </c>
       <c r="D30" t="n">
-        <v>18.71063488154634</v>
+        <v>3.04047816825128</v>
       </c>
       <c r="E30" t="n">
-        <v>11.44077434150358</v>
+        <v>1.859125830494332</v>
       </c>
       <c r="F30" t="n">
-        <v>10.77661297002282</v>
+        <v>1.751199607628708</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
